--- a/VT_REG1_TRA_V12.xlsx
+++ b/VT_REG1_TRA_V12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C486514-0DCD-4E0E-9F6D-9D4828F59558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57442FC9-87AB-4C6F-815E-16D275CF30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VT_REG1_TRA_V12.xlsx
+++ b/VT_REG1_TRA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57442FC9-87AB-4C6F-815E-16D275CF30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7707AC8-BC39-4F6B-88C7-92D7A4F444AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -2846,7 +2846,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3159,6 +3159,7 @@
     <xf numFmtId="0" fontId="22" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="22" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="24">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -5667,7 +5668,7 @@
         <f>[2]EB1!K20</f>
         <v>0</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="174">
         <f>[2]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
@@ -8472,8 +8473,8 @@
         <v>DTRAI</v>
       </c>
       <c r="E25" s="167">
-        <f>('EB1'!G$9*'EB1'!$L$31*F25/(K25*G25))*1.01</f>
-        <v>1196.526982608</v>
+        <f>('EB1'!L$9*'EB1'!$L$31*F25/(K25*G25))*1.01</f>
+        <v>25.363550663999998</v>
       </c>
       <c r="F25" s="168">
         <v>1</v>
@@ -8495,7 +8496,7 @@
       </c>
       <c r="M25" s="126">
         <f>E25*G25*K25*H25</f>
-        <v>59.826349130399997</v>
+        <v>1.2681775332</v>
       </c>
       <c r="O25" s="106" t="s">
         <v>97</v>
@@ -9262,7 +9263,7 @@
       </c>
       <c r="E15" s="59">
         <f>SUMIF(DemTechs_TRA!D$19:D$31,Demands!C15,DemTechs_TRA!M$19:M$31)</f>
-        <v>59.826349130399997</v>
+        <v>1.2681775332</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>120</v>
